--- a/data/dividends_info_20260331.xlsx
+++ b/data/dividends_info_20260331.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>27.2549991607666</v>
+        <v>28.60499954223633</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3302146496836236</v>
+        <v>0.3146303144214762</v>
       </c>
       <c r="J2" t="n">
         <v>349</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>51.15000152587891</v>
+        <v>50.90000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.368523908344051</v>
+        <v>1.375245538340704</v>
       </c>
       <c r="J3" t="n">
         <v>328</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>27.28000068664551</v>
+        <v>28.60499954223633</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3299120151564295</v>
+        <v>0.3146303144214762</v>
       </c>
       <c r="J5" t="n">
         <v>258</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.996000051498413</v>
+        <v>1.991999983787537</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85771533132955</v>
+        <v>3.865461878849728</v>
       </c>
       <c r="J6" t="n">
         <v>237</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5.489999771118164</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="I7" t="n">
-        <v>3.64298740142325</v>
+        <v>3.521126866979135</v>
       </c>
       <c r="J7" t="n">
         <v>230</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5.5</v>
+        <v>5.449999809265137</v>
       </c>
       <c r="I8" t="n">
-        <v>1.090909090909091</v>
+        <v>1.100917469721714</v>
       </c>
       <c r="J8" t="n">
         <v>202</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>27.28000068664551</v>
+        <v>28.60499954223633</v>
       </c>
       <c r="I9" t="n">
-        <v>0.3299120151564295</v>
+        <v>0.3146303144214762</v>
       </c>
       <c r="J9" t="n">
         <v>174</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>9.468000411987305</v>
+        <v>9.375</v>
       </c>
       <c r="I10" t="n">
-        <v>2.746091980211763</v>
+        <v>2.773333333333333</v>
       </c>
       <c r="J10" t="n">
         <v>111</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>16.20000076293945</v>
+        <v>16.45999908447266</v>
       </c>
       <c r="I11" t="n">
-        <v>3.703703529277682</v>
+        <v>3.645200688777698</v>
       </c>
       <c r="J11" t="n">
         <v>111</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>4.914999961853027</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="I13" t="n">
-        <v>2.441505614066337</v>
+        <v>2.362204759886205</v>
       </c>
       <c r="J13" t="n">
         <v>104</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>31.10000038146973</v>
+        <v>31.60000038146973</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4823151066241604</v>
+        <v>0.4746835385735</v>
       </c>
       <c r="J16" t="n">
         <v>97</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>22.1200008392334</v>
+        <v>22.29999923706055</v>
       </c>
       <c r="I17" t="n">
-        <v>1.130198872129266</v>
+        <v>1.121076271538714</v>
       </c>
       <c r="J17" t="n">
         <v>83</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>22.14999961853027</v>
+        <v>22.04999923706055</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8803611889765753</v>
+        <v>0.8843537720956184</v>
       </c>
       <c r="J18" t="n">
         <v>83</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>5.190000057220459</v>
+        <v>5.170000076293945</v>
       </c>
       <c r="I19" t="n">
-        <v>5.587668531844131</v>
+        <v>5.609284249912102</v>
       </c>
       <c r="J19" t="n">
         <v>83</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3.990000009536743</v>
+        <v>3.971999883651733</v>
       </c>
       <c r="I20" t="n">
-        <v>4.010025053072035</v>
+        <v>4.028197499666112</v>
       </c>
       <c r="J20" t="n">
         <v>83</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.450000047683716</v>
+        <v>2.437999963760376</v>
       </c>
       <c r="I21" t="n">
-        <v>5.657142747039352</v>
+        <v>5.684987779336267</v>
       </c>
       <c r="J21" t="n">
         <v>83</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>55.77999877929688</v>
+        <v>58.04000091552734</v>
       </c>
       <c r="I22" t="n">
-        <v>1.129437098937027</v>
+        <v>1.085458287495404</v>
       </c>
       <c r="J22" t="n">
         <v>83</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>20.18000030517578</v>
+        <v>20.13999938964844</v>
       </c>
       <c r="I24" t="n">
-        <v>4.212091115687403</v>
+        <v>4.220456930286121</v>
       </c>
       <c r="J24" t="n">
         <v>83</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>27.28000068664551</v>
+        <v>28.60499954223633</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3299120151564295</v>
+        <v>0.3146303144214762</v>
       </c>
       <c r="J25" t="n">
         <v>83</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>6.567999839782715</v>
+        <v>6.553999900817871</v>
       </c>
       <c r="I26" t="n">
-        <v>2.760353295106015</v>
+        <v>2.766249660415399</v>
       </c>
       <c r="J26" t="n">
         <v>83</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.894000053405762</v>
+        <v>9.86400032043457</v>
       </c>
       <c r="I28" t="n">
-        <v>2.799676556547518</v>
+        <v>2.808191311857099</v>
       </c>
       <c r="J28" t="n">
         <v>83</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>25.89999961853027</v>
+        <v>26.10000038146973</v>
       </c>
       <c r="I29" t="n">
-        <v>4.285714348836691</v>
+        <v>4.252873501059675</v>
       </c>
       <c r="J29" t="n">
         <v>65</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.824999988079071</v>
+        <v>0.8399999737739563</v>
       </c>
       <c r="I30" t="n">
-        <v>3.636363688907676</v>
+        <v>3.571428682933862</v>
       </c>
       <c r="J30" t="n">
         <v>62</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.4639999866485596</v>
+        <v>0.4650000035762787</v>
       </c>
       <c r="I31" t="n">
-        <v>4.956896694357135</v>
+        <v>4.946236521098666</v>
       </c>
       <c r="J31" t="n">
         <v>62</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2.529999971389771</v>
+        <v>2.565000057220459</v>
       </c>
       <c r="I32" t="n">
-        <v>7.114624586383811</v>
+        <v>7.017543703100556</v>
       </c>
       <c r="J32" t="n">
         <v>55</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>8.850000381469727</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I33" t="n">
-        <v>3.389830362359586</v>
+        <v>3.409090835200855</v>
       </c>
       <c r="J33" t="n">
         <v>55</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>12.17000007629395</v>
+        <v>12.28999996185303</v>
       </c>
       <c r="I34" t="n">
-        <v>2.054231704459701</v>
+        <v>2.034174131619006</v>
       </c>
       <c r="J34" t="n">
         <v>55</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>3.420000076293945</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="I35" t="n">
-        <v>4.385964814437847</v>
+        <v>4.411764582135689</v>
       </c>
       <c r="J35" t="n">
         <v>55</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>13.19999980926514</v>
+        <v>13.94999980926514</v>
       </c>
       <c r="I36" t="n">
-        <v>4.393939457430109</v>
+        <v>4.157706150037241</v>
       </c>
       <c r="J36" t="n">
         <v>55</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2.434000015258789</v>
+        <v>2.427999973297119</v>
       </c>
       <c r="I37" t="n">
-        <v>4.272801945276177</v>
+        <v>4.283360837882237</v>
       </c>
       <c r="J37" t="n">
         <v>48</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>9.310000419616699</v>
+        <v>9.39799976348877</v>
       </c>
       <c r="I38" t="n">
-        <v>3.11493004220444</v>
+        <v>3.085763005939307</v>
       </c>
       <c r="J38" t="n">
         <v>48</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1.996000051498413</v>
+        <v>1.991999983787537</v>
       </c>
       <c r="I39" t="n">
-        <v>3.85771533132955</v>
+        <v>3.865461878849728</v>
       </c>
       <c r="J39" t="n">
         <v>48</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>34.4900016784668</v>
+        <v>34.5099983215332</v>
       </c>
       <c r="I40" t="n">
-        <v>4.755001218291921</v>
+        <v>4.752245957012085</v>
       </c>
       <c r="J40" t="n">
         <v>48</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>32.02000045776367</v>
+        <v>32.34999847412109</v>
       </c>
       <c r="I41" t="n">
-        <v>6.246096100586012</v>
+        <v>6.182380507992705</v>
       </c>
       <c r="J41" t="n">
         <v>48</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>3.638000011444092</v>
+        <v>3.674000024795532</v>
       </c>
       <c r="I42" t="n">
-        <v>2.748763047977708</v>
+        <v>2.721829050765052</v>
       </c>
       <c r="J42" t="n">
         <v>48</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>31.95000076293945</v>
+        <v>33.09999847412109</v>
       </c>
       <c r="I43" t="n">
-        <v>0.464663525680434</v>
+        <v>0.4485196581385705</v>
       </c>
       <c r="J43" t="n">
         <v>48</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>21.55999946594238</v>
+        <v>20.97999954223633</v>
       </c>
       <c r="I44" t="n">
-        <v>4.267161515719393</v>
+        <v>4.385128789673625</v>
       </c>
       <c r="J44" t="n">
         <v>48</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>8.079999923706055</v>
+        <v>8.114999771118164</v>
       </c>
       <c r="I45" t="n">
-        <v>3.712871322186832</v>
+        <v>3.696857775248748</v>
       </c>
       <c r="J45" t="n">
         <v>48</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>73.83999633789062</v>
+        <v>74.58000183105469</v>
       </c>
       <c r="I46" t="n">
-        <v>1.408450774077746</v>
+        <v>1.394475696522375</v>
       </c>
       <c r="J46" t="n">
         <v>48</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>51.15000152587891</v>
+        <v>50.90000152587891</v>
       </c>
       <c r="I47" t="n">
-        <v>4.301075140509877</v>
+        <v>4.3222002633565</v>
       </c>
       <c r="J47" t="n">
         <v>48</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>7.418000221252441</v>
+        <v>7.427000045776367</v>
       </c>
       <c r="I48" t="n">
-        <v>11.5934210615971</v>
+        <v>11.57937248821037</v>
       </c>
       <c r="J48" t="n">
         <v>48</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>11.02499961853027</v>
+        <v>11.13500022888184</v>
       </c>
       <c r="I49" t="n">
-        <v>5.079365255113295</v>
+        <v>5.029187144042247</v>
       </c>
       <c r="J49" t="n">
         <v>48</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1.700000047683716</v>
+        <v>1.740000009536743</v>
       </c>
       <c r="I50" t="n">
-        <v>2.352941110472368</v>
+        <v>2.298850562112904</v>
       </c>
       <c r="J50" t="n">
         <v>48</v>
@@ -2826,10 +2826,10 @@
         </is>
       </c>
       <c r="H51" t="n">
-        <v>8.479999542236328</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="I51" t="n">
-        <v>3.537736040029132</v>
+        <v>3.496503527594645</v>
       </c>
       <c r="J51" t="n">
         <v>48</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.210000038146973</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I52" t="n">
-        <v>4.886877743701542</v>
+        <v>4.821428550901461</v>
       </c>
       <c r="J52" t="n">
         <v>48</v>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="H53" t="n">
-        <v>65.59999847412109</v>
+        <v>66.40000152587891</v>
       </c>
       <c r="I53" t="n">
-        <v>3.140243975482196</v>
+        <v>3.102409567260522</v>
       </c>
       <c r="J53" t="n">
         <v>48</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>14.4399995803833</v>
+        <v>14.52000045776367</v>
       </c>
       <c r="I54" t="n">
-        <v>5.193905968105934</v>
+        <v>5.165289093355255</v>
       </c>
       <c r="J54" t="n">
         <v>48</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>15.34000015258789</v>
+        <v>15.31999969482422</v>
       </c>
       <c r="I55" t="n">
-        <v>1.955671427743691</v>
+        <v>1.95822458208895</v>
       </c>
       <c r="J55" t="n">
         <v>48</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>41.40000152587891</v>
+        <v>41</v>
       </c>
       <c r="I56" t="n">
-        <v>2.05314002094582</v>
+        <v>2.073170731707317</v>
       </c>
       <c r="J56" t="n">
         <v>48</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>29.28000068664551</v>
+        <v>29.97999954223633</v>
       </c>
       <c r="I57" t="n">
-        <v>2.903005396402472</v>
+        <v>2.835223525612486</v>
       </c>
       <c r="J57" t="n">
         <v>48</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>59.47999954223633</v>
+        <v>59.97999954223633</v>
       </c>
       <c r="I58" t="n">
-        <v>2.18560862475609</v>
+        <v>2.167389146251284</v>
       </c>
       <c r="J58" t="n">
         <v>48</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="H59" t="n">
-        <v>6.980000019073486</v>
+        <v>7</v>
       </c>
       <c r="I59" t="n">
-        <v>8.595988515192627</v>
+        <v>8.571428571428571</v>
       </c>
       <c r="J59" t="n">
         <v>48</v>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="H60" t="n">
-        <v>5.489999771118164</v>
+        <v>5.679999828338623</v>
       </c>
       <c r="I60" t="n">
-        <v>3.64298740142325</v>
+        <v>3.521126866979135</v>
       </c>
       <c r="J60" t="n">
         <v>48</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>21.79999923706055</v>
+        <v>21.95999908447266</v>
       </c>
       <c r="I61" t="n">
-        <v>4.587156123840477</v>
+        <v>4.553734251779063</v>
       </c>
       <c r="J61" t="n">
         <v>48</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>4.199999809265137</v>
+        <v>4.159999847412109</v>
       </c>
       <c r="I62" t="n">
-        <v>5.119047851519261</v>
+        <v>5.168269420340224</v>
       </c>
       <c r="J62" t="n">
         <v>48</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>9.210000038146973</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I63" t="n">
-        <v>2.605863181389165</v>
+        <v>2.608695706257524</v>
       </c>
       <c r="J63" t="n">
         <v>48</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>19.02499961853027</v>
+        <v>18.93499946594238</v>
       </c>
       <c r="I64" t="n">
-        <v>4.15243109508682</v>
+        <v>4.172168060637873</v>
       </c>
       <c r="J64" t="n">
         <v>48</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>4.559999942779541</v>
+        <v>4.610000133514404</v>
       </c>
       <c r="I65" t="n">
-        <v>2.039473709802549</v>
+        <v>2.017353520749294</v>
       </c>
       <c r="J65" t="n">
         <v>48</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>5.5</v>
+        <v>5.449999809265137</v>
       </c>
       <c r="I66" t="n">
-        <v>1.090909090909091</v>
+        <v>1.100917469721714</v>
       </c>
       <c r="J66" t="n">
         <v>48</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>32.81999969482422</v>
+        <v>32.40000152587891</v>
       </c>
       <c r="I67" t="n">
-        <v>1.066422922774115</v>
+        <v>1.080246862705991</v>
       </c>
       <c r="J67" t="n">
         <v>48</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1.950000047683716</v>
+        <v>2.009999990463257</v>
       </c>
       <c r="I68" t="n">
-        <v>3.076923001682502</v>
+        <v>2.985074641028801</v>
       </c>
       <c r="J68" t="n">
         <v>48</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>11.69999980926514</v>
+        <v>11.80000019073486</v>
       </c>
       <c r="I69" t="n">
-        <v>1.70940173726859</v>
+        <v>1.694915226840727</v>
       </c>
       <c r="J69" t="n">
         <v>48</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>5.554999828338623</v>
+        <v>5.579999923706055</v>
       </c>
       <c r="I70" t="n">
-        <v>1.85418547584015</v>
+        <v>1.845878161438947</v>
       </c>
       <c r="J70" t="n">
         <v>48</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>5.144999980926514</v>
+        <v>5.160999774932861</v>
       </c>
       <c r="I71" t="n">
-        <v>3.692905747412359</v>
+        <v>3.681457242506307</v>
       </c>
       <c r="J71" t="n">
         <v>48</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>10.03999996185303</v>
+        <v>10.02999973297119</v>
       </c>
       <c r="I72" t="n">
-        <v>4.302788860969957</v>
+        <v>4.307078878376285</v>
       </c>
       <c r="J72" t="n">
         <v>48</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>24.81999969482422</v>
+        <v>24.76000022888184</v>
       </c>
       <c r="I73" t="n">
-        <v>1.772763921877704</v>
+        <v>1.777059757401587</v>
       </c>
       <c r="J73" t="n">
         <v>48</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>7.590000152587891</v>
+        <v>7.539999961853027</v>
       </c>
       <c r="I74" t="n">
-        <v>6.192358241781438</v>
+        <v>6.233421782199757</v>
       </c>
       <c r="J74" t="n">
         <v>48</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>50.88000106811523</v>
+        <v>51.40000152587891</v>
       </c>
       <c r="I75" t="n">
-        <v>2.751572269280734</v>
+        <v>2.723735327702523</v>
       </c>
       <c r="J75" t="n">
         <v>48</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>3.151999950408936</v>
+        <v>3.180000066757202</v>
       </c>
       <c r="I76" t="n">
-        <v>9.517766647206908</v>
+        <v>9.433962066105373</v>
       </c>
       <c r="J76" t="n">
         <v>48</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>11.10000038146973</v>
+        <v>11.39999961853027</v>
       </c>
       <c r="I77" t="n">
-        <v>1.081081043927956</v>
+        <v>1.052631614170798</v>
       </c>
       <c r="J77" t="n">
         <v>48</v>
@@ -4095,10 +4095,10 @@
         </is>
       </c>
       <c r="H78" t="n">
-        <v>3.400000095367432</v>
+        <v>3.5</v>
       </c>
       <c r="I78" t="n">
-        <v>4.999999859753782</v>
+        <v>4.857142857142858</v>
       </c>
       <c r="J78" t="n">
         <v>48</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>22.29999923706055</v>
+        <v>22.70000076293945</v>
       </c>
       <c r="I79" t="n">
-        <v>3.139013560308399</v>
+        <v>3.083700336886491</v>
       </c>
       <c r="J79" t="n">
         <v>48</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>3.029999971389771</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="I80" t="n">
-        <v>1.155115522458126</v>
+        <v>1.132686115604929</v>
       </c>
       <c r="J80" t="n">
         <v>48</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>0.921999990940094</v>
+        <v>0.9490000009536743</v>
       </c>
       <c r="I82" t="n">
-        <v>7.592190963974551</v>
+        <v>7.376185450964723</v>
       </c>
       <c r="J82" t="n">
         <v>48</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>48.88000106811523</v>
+        <v>49.04000091552734</v>
       </c>
       <c r="I83" t="n">
-        <v>1.452536793136729</v>
+        <v>1.447797689121159</v>
       </c>
       <c r="J83" t="n">
         <v>48</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>80.25</v>
+        <v>80.75</v>
       </c>
       <c r="I84" t="n">
-        <v>1.682242990654206</v>
+        <v>1.671826625386997</v>
       </c>
       <c r="J84" t="n">
         <v>48</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>7</v>
+        <v>7.21999979019165</v>
       </c>
       <c r="I85" t="n">
-        <v>1.142857142857143</v>
+        <v>1.108033273195932</v>
       </c>
       <c r="J85" t="n">
         <v>48</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>3.832000017166138</v>
+        <v>3.914000034332275</v>
       </c>
       <c r="I86" t="n">
-        <v>4.436325658623544</v>
+        <v>4.343382690567652</v>
       </c>
       <c r="J86" t="n">
         <v>48</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>58.20000076293945</v>
+        <v>58.90000152587891</v>
       </c>
       <c r="I88" t="n">
-        <v>0.7731958661528929</v>
+        <v>0.7640067713789165</v>
       </c>
       <c r="J88" t="n">
         <v>48</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>4.954999923706055</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="I89" t="n">
-        <v>0.8072654009262286</v>
+        <v>0.7812500174622986</v>
       </c>
       <c r="J89" t="n">
         <v>48</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>30.5</v>
+        <v>30.79999923706055</v>
       </c>
       <c r="I90" t="n">
-        <v>3.442622950819672</v>
+        <v>3.409090993536689</v>
       </c>
       <c r="J90" t="n">
         <v>48</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>17.27000045776367</v>
+        <v>17.34000015258789</v>
       </c>
       <c r="I92" t="n">
-        <v>2.200347364954309</v>
+        <v>2.191464801938236</v>
       </c>
       <c r="J92" t="n">
         <v>48</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>25.05999946594238</v>
+        <v>25.5</v>
       </c>
       <c r="I93" t="n">
-        <v>2.394253841926157</v>
+        <v>2.352941176470588</v>
       </c>
       <c r="J93" t="n">
         <v>48</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>29</v>
+        <v>29.60000038146973</v>
       </c>
       <c r="I94" t="n">
-        <v>1.206896551724138</v>
+        <v>1.182432417193846</v>
       </c>
       <c r="J94" t="n">
         <v>48</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>19.81500053405762</v>
+        <v>19.84499931335449</v>
       </c>
       <c r="I95" t="n">
-        <v>5.652283471176127</v>
+        <v>5.643739172348106</v>
       </c>
       <c r="J95" t="n">
         <v>48</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1.279999971389771</v>
+        <v>1.259999990463257</v>
       </c>
       <c r="I96" t="n">
-        <v>7.812500174622987</v>
+        <v>7.936507996578126</v>
       </c>
       <c r="J96" t="n">
         <v>48</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>2.278000116348267</v>
+        <v>2.26200008392334</v>
       </c>
       <c r="I97" t="n">
-        <v>11.41352004919084</v>
+        <v>11.4942524471105</v>
       </c>
       <c r="J97" t="n">
         <v>48</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>1.993000030517578</v>
+        <v>1.991999983787537</v>
       </c>
       <c r="I98" t="n">
-        <v>4.63120916139825</v>
+        <v>4.633534174257532</v>
       </c>
       <c r="J98" t="n">
         <v>48</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>9.140000343322754</v>
+        <v>9.039999961853027</v>
       </c>
       <c r="I99" t="n">
-        <v>3.829321519180174</v>
+        <v>3.871681432266917</v>
       </c>
       <c r="J99" t="n">
         <v>41</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>4.5</v>
+        <v>4.320000171661377</v>
       </c>
       <c r="I100" t="n">
-        <v>2.133333333333333</v>
+        <v>2.222222133919048</v>
       </c>
       <c r="J100" t="n">
         <v>41</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>5.940000057220459</v>
+        <v>5.840000152587891</v>
       </c>
       <c r="I101" t="n">
-        <v>5.050505001853162</v>
+        <v>5.136986167150362</v>
       </c>
       <c r="J101" t="n">
         <v>41</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>11.60000038146973</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I102" t="n">
-        <v>1.724137874335655</v>
+        <v>1.70940173726859</v>
       </c>
       <c r="J102" t="n">
         <v>41</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>14.61999988555908</v>
+        <v>14.96000003814697</v>
       </c>
       <c r="I105" t="n">
-        <v>3.419972666989385</v>
+        <v>3.342245980782315</v>
       </c>
       <c r="J105" t="n">
         <v>41</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>10.10000038146973</v>
+        <v>9.649999618530273</v>
       </c>
       <c r="I106" t="n">
-        <v>0.8415841266298152</v>
+        <v>0.880829050363691</v>
       </c>
       <c r="J106" t="n">
         <v>41</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>4.480000019073486</v>
+        <v>4.349999904632568</v>
       </c>
       <c r="I107" t="n">
-        <v>2.120535705257587</v>
+        <v>2.183908093856024</v>
       </c>
       <c r="J107" t="n">
         <v>41</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>1.080000042915344</v>
+        <v>1.110000014305115</v>
       </c>
       <c r="I108" t="n">
-        <v>2.77777766739881</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J108" t="n">
         <v>41</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>7.050000190734863</v>
+        <v>6.960000038146973</v>
       </c>
       <c r="I109" t="n">
-        <v>3.120567291460854</v>
+        <v>3.160919522905243</v>
       </c>
       <c r="J109" t="n">
         <v>41</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>3.365000009536743</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="I110" t="n">
-        <v>4.754829109852724</v>
+        <v>4.719763865745447</v>
       </c>
       <c r="J110" t="n">
         <v>34</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>19.42000007629395</v>
+        <v>20.39999961853027</v>
       </c>
       <c r="I111" t="n">
-        <v>3.14109164574427</v>
+        <v>2.990196134346534</v>
       </c>
       <c r="J111" t="n">
         <v>34</v>
@@ -5740,10 +5740,10 @@
         </is>
       </c>
       <c r="H113" t="n">
-        <v>11.5</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I113" t="n">
-        <v>6.08695652173913</v>
+        <v>5.982906080440066</v>
       </c>
       <c r="J113" t="n">
         <v>34</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>8.5</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I114" t="n">
-        <v>6.005882352941176</v>
+        <v>5.93604624832303</v>
       </c>
       <c r="J114" t="n">
         <v>34</v>
@@ -5834,10 +5834,10 @@
         </is>
       </c>
       <c r="H115" t="n">
-        <v>7.244999885559082</v>
+        <v>7.480000019073486</v>
       </c>
       <c r="I115" t="n">
-        <v>3.726708133400677</v>
+        <v>3.609625659244901</v>
       </c>
       <c r="J115" t="n">
         <v>34</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>4.885000228881836</v>
+        <v>4.929999828338623</v>
       </c>
       <c r="I116" t="n">
-        <v>7.164789838302917</v>
+        <v>7.099391727929281</v>
       </c>
       <c r="J116" t="n">
         <v>34</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>37.79999923706055</v>
+        <v>37.59999847412109</v>
       </c>
       <c r="I117" t="n">
-        <v>2.910052968788207</v>
+        <v>2.925532033617224</v>
       </c>
       <c r="J117" t="n">
         <v>34</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>18.89999961853027</v>
+        <v>19</v>
       </c>
       <c r="I118" t="n">
-        <v>3.968254048347555</v>
+        <v>3.947368421052631</v>
       </c>
       <c r="J118" t="n">
         <v>34</v>
@@ -6022,10 +6022,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>10.14999961853027</v>
+        <v>9.899999618530273</v>
       </c>
       <c r="I119" t="n">
-        <v>4.23645336119002</v>
+        <v>4.343434510796846</v>
       </c>
       <c r="J119" t="n">
         <v>34</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>3.930000066757202</v>
+        <v>3.954999923706055</v>
       </c>
       <c r="I120" t="n">
-        <v>3.816793828295553</v>
+        <v>3.792667582644139</v>
       </c>
       <c r="J120" t="n">
         <v>34</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>12.65999984741211</v>
+        <v>12.39999961853027</v>
       </c>
       <c r="I121" t="n">
-        <v>1.557417080382542</v>
+        <v>1.590072629561659</v>
       </c>
       <c r="J121" t="n">
         <v>34</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>26.64999961853027</v>
+        <v>26.35000038146973</v>
       </c>
       <c r="I122" t="n">
-        <v>4.127579796418265</v>
+        <v>4.174572994593047</v>
       </c>
       <c r="J122" t="n">
         <v>34</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>18.79999923706055</v>
+        <v>18.60000038146973</v>
       </c>
       <c r="I123" t="n">
-        <v>2.659574576015658</v>
+        <v>2.688171987878697</v>
       </c>
       <c r="J123" t="n">
         <v>34</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="H124" t="n">
-        <v>38.20000076293945</v>
+        <v>39.34999847412109</v>
       </c>
       <c r="I124" t="n">
-        <v>1.230366467573426</v>
+        <v>1.194409194981545</v>
       </c>
       <c r="J124" t="n">
         <v>34</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>2.569999933242798</v>
+        <v>2.5</v>
       </c>
       <c r="I125" t="n">
-        <v>4.280155753202811</v>
+        <v>4.399999999999999</v>
       </c>
       <c r="J125" t="n">
         <v>34</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>75.90000152587891</v>
+        <v>78.69999694824219</v>
       </c>
       <c r="I126" t="n">
-        <v>1.581027636199516</v>
+        <v>1.524777695721121</v>
       </c>
       <c r="J126" t="n">
         <v>34</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>23.95000076293945</v>
+        <v>23.64999961853027</v>
       </c>
       <c r="I127" t="n">
-        <v>1.127348607093999</v>
+        <v>1.141649067040362</v>
       </c>
       <c r="J127" t="n">
         <v>34</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>10.39999961853027</v>
+        <v>10</v>
       </c>
       <c r="I128" t="n">
-        <v>3.653846287868437</v>
+        <v>3.8</v>
       </c>
       <c r="J128" t="n">
         <v>34</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>25.95000076293945</v>
+        <v>26.14999961853027</v>
       </c>
       <c r="I129" t="n">
-        <v>1.15606933017299</v>
+        <v>1.147227550196275</v>
       </c>
       <c r="J129" t="n">
         <v>34</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>0.1504999995231628</v>
+        <v>0.1490000039339066</v>
       </c>
       <c r="I130" t="n">
-        <v>4.651162805434201</v>
+        <v>4.6979864531447</v>
       </c>
       <c r="J130" t="n">
         <v>27</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>2.279999971389771</v>
+        <v>2.269999980926514</v>
       </c>
       <c r="I132" t="n">
-        <v>2.850877228756251</v>
+        <v>2.863436147407802</v>
       </c>
       <c r="J132" t="n">
         <v>27</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>7.119999885559082</v>
+        <v>7.150000095367432</v>
       </c>
       <c r="I133" t="n">
-        <v>3.511236011492847</v>
+        <v>3.496503449866776</v>
       </c>
       <c r="J133" t="n">
         <v>27</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>1.320000052452087</v>
+        <v>1.25</v>
       </c>
       <c r="I134" t="n">
-        <v>5.30303009230682</v>
+        <v>5.600000000000001</v>
       </c>
       <c r="J134" t="n">
         <v>27</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>6.630000114440918</v>
+        <v>6.574999809265137</v>
       </c>
       <c r="I135" t="n">
-        <v>7.541477999539417</v>
+        <v>7.604562958244149</v>
       </c>
       <c r="J135" t="n">
         <v>20</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>17.35000038146973</v>
+        <v>17.28000068664551</v>
       </c>
       <c r="I136" t="n">
-        <v>3.746397612153471</v>
+        <v>3.761573924602556</v>
       </c>
       <c r="J136" t="n">
         <v>20</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>11.89000034332275</v>
+        <v>11.85999965667725</v>
       </c>
       <c r="I137" t="n">
-        <v>4.541631492073555</v>
+        <v>4.55311986198901</v>
       </c>
       <c r="J137" t="n">
         <v>20</v>
@@ -6915,10 +6915,10 @@
         </is>
       </c>
       <c r="H138" t="n">
-        <v>6.188000202178955</v>
+        <v>6.130000114440918</v>
       </c>
       <c r="I138" t="n">
-        <v>1.616030974995563</v>
+        <v>1.631321339854827</v>
       </c>
       <c r="J138" t="n">
         <v>20</v>
@@ -6962,10 +6962,10 @@
         </is>
       </c>
       <c r="H139" t="n">
-        <v>8.260000228881836</v>
+        <v>8.399999618530273</v>
       </c>
       <c r="I139" t="n">
-        <v>1.93704595116772</v>
+        <v>1.904761991262981</v>
       </c>
       <c r="J139" t="n">
         <v>20</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>288.2000122070312</v>
+        <v>289</v>
       </c>
       <c r="I140" t="n">
-        <v>1.254337212658801</v>
+        <v>1.250865051903114</v>
       </c>
       <c r="J140" t="n">
         <v>20</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>26</v>
+        <v>26.5</v>
       </c>
       <c r="I141" t="n">
-        <v>5.230769230769231</v>
+        <v>5.132075471698114</v>
       </c>
       <c r="J141" t="n">
         <v>20</v>
@@ -7103,10 +7103,10 @@
         </is>
       </c>
       <c r="H142" t="n">
-        <v>13.07999992370605</v>
+        <v>13.30000019073486</v>
       </c>
       <c r="I142" t="n">
-        <v>4.472477090307563</v>
+        <v>4.398496177522814</v>
       </c>
       <c r="J142" t="n">
         <v>20</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>95.31999969482422</v>
+        <v>98.77999877929688</v>
       </c>
       <c r="I144" t="n">
-        <v>0.9441880013443485</v>
+        <v>0.9111156217068404</v>
       </c>
       <c r="J144" t="n">
         <v>20</v>
@@ -7244,10 +7244,10 @@
         </is>
       </c>
       <c r="H145" t="n">
-        <v>60.52999877929688</v>
+        <v>60.86000061035156</v>
       </c>
       <c r="I145" t="n">
-        <v>2.842887881551662</v>
+        <v>2.827472860240676</v>
       </c>
       <c r="J145" t="n">
         <v>20</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>23</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="I146" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6140351082662987</v>
       </c>
       <c r="J146" t="n">
         <v>13</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>24.28000068664551</v>
+        <v>24.85000038146973</v>
       </c>
       <c r="I149" t="n">
-        <v>1.070840167409902</v>
+        <v>1.046277649934678</v>
       </c>
       <c r="J149" t="n">
         <v>-8</v>
@@ -7479,10 +7479,10 @@
         </is>
       </c>
       <c r="H150" t="n">
-        <v>27.28000068664551</v>
+        <v>28.60499954223633</v>
       </c>
       <c r="I150" t="n">
-        <v>0.3299120151564295</v>
+        <v>0.3146303144214762</v>
       </c>
       <c r="J150" t="n">
         <v>-8</v>
@@ -8970,7 +8970,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -8980,14 +8980,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8997,14 +8997,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9014,7 +9014,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9089,7 +9089,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -9123,7 +9123,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -9157,7 +9157,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -9174,7 +9174,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -9191,7 +9191,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -9208,7 +9208,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9218,14 +9218,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9235,14 +9235,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9252,14 +9252,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9269,14 +9269,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9310,7 +9310,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9320,14 +9320,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9337,14 +9337,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -9361,7 +9361,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -9371,14 +9371,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -9388,14 +9388,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -9405,14 +9405,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -9422,14 +9422,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -9439,14 +9439,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -9456,14 +9456,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -9473,7 +9473,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -9514,7 +9514,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -9531,7 +9531,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -9548,7 +9548,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -9558,14 +9558,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>CALTAGIRONE EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -9575,14 +9575,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -9599,7 +9599,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -9616,7 +9616,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -9633,7 +9633,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>CALTAGIRONE EDITORE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -9650,7 +9650,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -9660,14 +9660,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -9677,14 +9677,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -9701,7 +9701,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -9718,7 +9718,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -9735,7 +9735,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -9752,7 +9752,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -9769,7 +9769,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9779,14 +9779,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -9796,14 +9796,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9813,14 +9813,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9830,14 +9830,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9847,14 +9847,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9888,7 +9888,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9905,7 +9905,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9922,7 +9922,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9939,7 +9939,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9956,7 +9956,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9973,7 +9973,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -9990,7 +9990,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -10007,7 +10007,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -10017,14 +10017,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10068,14 +10068,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10092,7 +10092,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10109,7 +10109,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10126,7 +10126,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10143,7 +10143,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10153,7 +10153,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10194,7 +10194,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10211,7 +10211,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10228,7 +10228,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10245,7 +10245,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10262,7 +10262,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10279,7 +10279,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10289,14 +10289,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10313,7 +10313,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10330,7 +10330,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10347,7 +10347,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10364,7 +10364,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -10381,7 +10381,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -10398,7 +10398,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10408,14 +10408,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10432,7 +10432,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10442,14 +10442,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10466,7 +10466,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10483,7 +10483,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10500,7 +10500,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10517,7 +10517,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -10551,7 +10551,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -10568,7 +10568,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -10578,14 +10578,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -10595,14 +10595,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10619,7 +10619,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -10629,14 +10629,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -10646,14 +10646,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -10663,14 +10663,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -10687,7 +10687,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -10697,14 +10697,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -10714,14 +10714,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -10738,7 +10738,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -10748,14 +10748,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -10772,7 +10772,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -10782,14 +10782,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -10823,7 +10823,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -10874,7 +10874,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -10891,7 +10891,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -10908,7 +10908,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -10925,7 +10925,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -10942,7 +10942,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -10952,14 +10952,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -10976,7 +10976,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -10993,7 +10993,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -11010,7 +11010,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -11020,14 +11020,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -11037,14 +11037,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -11061,7 +11061,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -11078,7 +11078,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -11095,7 +11095,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -11112,7 +11112,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -11122,14 +11122,14 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -11139,14 +11139,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -11163,7 +11163,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -11180,7 +11180,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -11197,7 +11197,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>SOGEFI S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -11214,7 +11214,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>SOGEFI S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -11231,7 +11231,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -11248,7 +11248,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -11265,7 +11265,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -11282,7 +11282,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -11299,7 +11299,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -11316,7 +11316,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -11333,7 +11333,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -11350,7 +11350,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -11384,7 +11384,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -11394,14 +11394,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -11418,7 +11418,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -11435,7 +11435,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -11452,7 +11452,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -11469,7 +11469,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -11486,7 +11486,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -11503,7 +11503,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -11520,7 +11520,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -11537,7 +11537,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -11554,7 +11554,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -11571,7 +11571,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -11588,7 +11588,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -11598,14 +11598,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -11622,7 +11622,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -11639,7 +11639,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -11649,14 +11649,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -11673,7 +11673,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -11690,7 +11690,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -11700,14 +11700,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -11724,7 +11724,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -11741,7 +11741,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -11751,14 +11751,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -11775,7 +11775,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -11792,7 +11792,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -11809,7 +11809,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -11826,7 +11826,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -11843,7 +11843,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -11860,7 +11860,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -11877,7 +11877,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -11894,7 +11894,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -11911,7 +11911,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -11921,14 +11921,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -11938,14 +11938,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -11962,7 +11962,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -11979,7 +11979,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -11996,7 +11996,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -12013,7 +12013,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -12030,7 +12030,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -12047,7 +12047,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -12064,7 +12064,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -12081,7 +12081,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -12098,7 +12098,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -12115,7 +12115,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -12132,7 +12132,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -12149,7 +12149,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -12159,14 +12159,14 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -12176,14 +12176,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -12200,7 +12200,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -12217,7 +12217,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -12227,14 +12227,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -12251,7 +12251,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -12268,7 +12268,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -12278,14 +12278,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -12302,7 +12302,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -12319,7 +12319,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -12336,7 +12336,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -12346,14 +12346,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -12363,14 +12363,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -12387,7 +12387,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -12404,7 +12404,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -12421,7 +12421,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -12431,14 +12431,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -12448,14 +12448,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -12472,7 +12472,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -12489,7 +12489,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -12506,7 +12506,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -12523,7 +12523,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -12540,7 +12540,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -12557,7 +12557,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>MAIRE S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -12567,14 +12567,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -12584,14 +12584,14 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -12608,7 +12608,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -12625,7 +12625,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -12635,14 +12635,14 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -12659,7 +12659,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -12676,7 +12676,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -12693,7 +12693,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -12703,14 +12703,14 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -12727,7 +12727,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -12737,14 +12737,14 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -12761,7 +12761,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -12771,14 +12771,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -12795,7 +12795,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -12812,7 +12812,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -12829,7 +12829,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -12846,7 +12846,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -12856,14 +12856,14 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -12880,7 +12880,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -12890,14 +12890,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -12914,7 +12914,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -12931,7 +12931,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -12948,7 +12948,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -12965,7 +12965,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -12982,7 +12982,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -12992,14 +12992,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -13016,7 +13016,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -13026,14 +13026,14 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -13050,7 +13050,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -13067,7 +13067,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -13084,7 +13084,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -13101,7 +13101,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -13111,14 +13111,14 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -13135,7 +13135,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -13152,7 +13152,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -13169,7 +13169,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -13186,7 +13186,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -13203,7 +13203,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -13220,7 +13220,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -13230,14 +13230,14 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -13247,14 +13247,14 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -13271,7 +13271,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -13288,7 +13288,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -13305,7 +13305,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -13322,7 +13322,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -13339,7 +13339,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -13356,7 +13356,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -13373,7 +13373,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -13383,14 +13383,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -13407,7 +13407,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -13417,14 +13417,14 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -13441,7 +13441,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -13458,7 +13458,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -13475,7 +13475,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -13492,7 +13492,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -13509,7 +13509,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -13526,7 +13526,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -13543,7 +13543,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -13553,14 +13553,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -13577,7 +13577,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -13594,7 +13594,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -13611,7 +13611,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -13621,14 +13621,14 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -13638,14 +13638,14 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -13662,7 +13662,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -13672,14 +13672,14 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -13696,7 +13696,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -13706,14 +13706,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -13730,7 +13730,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -13747,7 +13747,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -13757,14 +13757,14 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -13781,7 +13781,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -13798,7 +13798,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -13815,7 +13815,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -13832,7 +13832,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -13849,7 +13849,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -13866,7 +13866,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -13883,7 +13883,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -13900,7 +13900,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -13917,7 +13917,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -13951,7 +13951,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -13961,14 +13961,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -13985,7 +13985,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -14002,7 +14002,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -14019,7 +14019,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -14029,14 +14029,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -14046,14 +14046,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -14070,7 +14070,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -14087,7 +14087,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -14104,7 +14104,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -14121,7 +14121,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -14138,7 +14138,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -14155,7 +14155,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -14172,7 +14172,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -14189,7 +14189,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -14206,7 +14206,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -14223,7 +14223,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -14233,14 +14233,14 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -14257,7 +14257,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -14274,7 +14274,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -14291,7 +14291,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -14301,14 +14301,14 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -14342,7 +14342,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -14359,7 +14359,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -14369,14 +14369,14 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -14386,14 +14386,14 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -14410,7 +14410,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -14427,7 +14427,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -14444,7 +14444,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -14461,7 +14461,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -14478,7 +14478,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -14495,7 +14495,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -14512,7 +14512,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -14529,7 +14529,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -14546,7 +14546,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -14563,7 +14563,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -14580,7 +14580,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -14597,7 +14597,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -14614,7 +14614,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -14631,7 +14631,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -14648,7 +14648,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -14658,14 +14658,14 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -14682,7 +14682,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -14699,7 +14699,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -14716,7 +14716,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -14733,7 +14733,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -14750,7 +14750,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -14767,7 +14767,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -14784,7 +14784,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -14801,7 +14801,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -14811,14 +14811,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -14835,7 +14835,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -14852,7 +14852,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -14862,14 +14862,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -14879,14 +14879,14 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -14903,7 +14903,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -14920,7 +14920,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -14937,7 +14937,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -14954,7 +14954,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -14964,14 +14964,14 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -14981,14 +14981,14 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -14998,14 +14998,14 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -15022,7 +15022,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -15039,7 +15039,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -15073,7 +15073,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -15090,7 +15090,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -15107,7 +15107,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -15124,7 +15124,7 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -15141,7 +15141,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -15158,7 +15158,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -15175,7 +15175,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -15185,14 +15185,14 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -15209,7 +15209,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -15226,7 +15226,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -15236,14 +15236,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -15253,14 +15253,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -15277,7 +15277,7 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -15294,7 +15294,7 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -15319,608 +15319,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005600249</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-05-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8.850000381469727</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3.389830362359586</v>
-      </c>
-      <c r="I2" t="n">
-        <v>55</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>GPI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005221517</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-07-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>16.20000076293945</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>3.703703529277682</v>
-      </c>
-      <c r="I3" t="n">
-        <v>111</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ILPRA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IT0005359101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1.090909090909091</v>
-      </c>
-      <c r="I4" t="n">
-        <v>48</v>
-      </c>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ILPRA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>IT0005359101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>2026-10-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1.090909090909091</v>
-      </c>
-      <c r="I5" t="n">
-        <v>202</v>
-      </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>IT0005037905</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>11.60000038146973</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1.724137874335655</v>
-      </c>
-      <c r="I6" t="n">
-        <v>41</v>
-      </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Italian Wine Brands S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>IT0005075764</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>2026-05-04 00:00:00</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>18.79999923706055</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>2.659574576015658</v>
-      </c>
-      <c r="I7" t="n">
-        <v>34</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>IT0004376858</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2.160000085830688</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>2.77777766739881</v>
-      </c>
-      <c r="I8" t="n">
-        <v>41</v>
-      </c>
-      <c r="J8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>PHILOGEN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>IT0005373789</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>22.29999923706055</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>3.139013560308399</v>
-      </c>
-      <c r="I9" t="n">
-        <v>48</v>
-      </c>
-      <c r="J9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SBE-Varvit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>IT0005568461</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>7.599999904632568</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.297</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>3.907894785879722</v>
-      </c>
-      <c r="I10" t="n">
-        <v>48</v>
-      </c>
-      <c r="J10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>IT0005521551</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2026-05-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1.080000042915344</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>2.77777766739881</v>
-      </c>
-      <c r="I11" t="n">
-        <v>41</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Smart Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>IT0005621070</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1.600000023841858</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>3.124999953433872</v>
-      </c>
-      <c r="I12" t="n">
-        <v>48</v>
-      </c>
-      <c r="J12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>IT0004717200</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>1.279999971389771</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>7.812500174622987</v>
-      </c>
-      <c r="I13" t="n">
-        <v>48</v>
-      </c>
-      <c r="J13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>doValue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>IT0005610958</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>2026-05-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>1.993000030517578</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.09229999999999999</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>4.63120916139825</v>
-      </c>
-      <c r="I14" t="n">
-        <v>48</v>
-      </c>
-      <c r="J14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15931,1880 +15332,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>AATECH S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ACQUAZZURRA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Arterra Bioscience S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Basic Net S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CELLULARLINE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CEMBRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CleanBnB S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Cogefeed S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Com.Tel S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Copernico SIM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DHH S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Datrix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Datrix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>DigiTouch S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>E.P.H. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>ESI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Emma Villas S.p.A.</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Energy S.p.A.</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>ErreDue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Estrima S.p.A.</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Execus S.p.A.</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>FRANCHETTI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>First Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>GEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>GPI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>GREEN OLEO S.p.A</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Gentili Mosconi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Gismondi 1754 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>ILPRA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>IMMSI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>INWIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>IRCE s.p.a</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>International Care Company S.p.A.</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Italian Wine Brands S.p.A.</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Litix S.p.A.</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Lucisano Media Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Maps S.p.A.</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Novamarine S.p.A.</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>OPS Retail S.p.A.</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>PHILOGEN S.p.A.</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>PLANETEL S.p.A.</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>PLC S.p.A.</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>PREMIA FINANCE S.P.A</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>PREMIA FINANCE S.P.A</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Pasquarelli Auto S.p.A.</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Porto Aviation Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Pozzi Milano S.p.A.</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>RECORDATI S.p.A.</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>ROSETTI MARINO S.p.A.</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Racing Force S.p.A.</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Redelfi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Redelfi S.p.A.</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Reway Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>SABAF S.p.A.</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>SBE-Varvit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>SOGES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>SOGES GROUP S.p.A.</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STAR7 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Smart Capital S.p.A.</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Snam S.p.A.</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Softlab S.p.A.</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Solid World Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Somec S.p.A.</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Stellantis N.V.</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>T.P.S. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>TMP Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Tecno S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>TradeLab S.p.A.</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>UCapital24 S.p.A.</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>VALTECNE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Valica S.p.A.</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Vantea Smart S.p.A.</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Vimi Fasteners S.p.A.</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>WEBSOLUTE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>doxee S.p.A.</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>iVision Tech S.p.A.</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>